--- a/output/invoice_info_db/未匹配清单_发票信息_2026_20260619.xlsx
+++ b/output/invoice_info_db/未匹配清单_发票信息_2026_20260619.xlsx
@@ -456,17 +456,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39085</v>
+        <v>39121</v>
       </c>
       <c r="C2" t="n">
         <v>1150</v>
       </c>
       <c r="D2" t="n">
-        <v>40235</v>
+        <v>40271</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.14%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
